--- a/order_generation/PO_excel_export/factory-6.xlsx
+++ b/order_generation/PO_excel_export/factory-6.xlsx
@@ -339,6 +339,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -731,7 +761,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>宁波瑾秀制刷科技有限公司</t>
+          <t>和鑫制刷厂</t>
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
@@ -757,7 +787,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>电话: +86-574-27889688   传真: +86-574-27889677</t>
+          <t>15105029337</t>
         </is>
       </c>
       <c r="C4" s="16" t="n"/>
@@ -783,7 +813,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>多多</t>
+          <t>朱春景</t>
         </is>
       </c>
       <c r="C5" s="16" t="n"/>
@@ -842,24 +872,20 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>ST1122-2</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>[图片未找到] [图片未找到]</t>
-        </is>
-      </c>
+          <t>US-RB01-01</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n"/>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>透明尼龙针+猪鬃.深棕色胶皮（TPR）带纹路模具更新（7589C），0.7mm透明尼龙针+猪鬃，棕色染头（7589C）. 包装方式：散货</t>
+          <t>禾木清洁刷清漆，3.1*7.3*1.1 厘米48孔。尼龙刷毛出峰2.5cm，加粗0.7mm，刷子表面和刷面清洁不要有碎屑附着,背后要加印logo Norsewood激光logo,散货</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>3.6</v>
+        <v>10.8</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
@@ -867,7 +893,7 @@
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>散货</t>
+          <t>如描述中要求</t>
         </is>
       </c>
       <c r="H7" s="20" t="n"/>
@@ -930,7 +956,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>宁波市海曙区高桥镇秀丰路67号1栋1楼，小张，18668289261</t>
+          <t>做好发到 小张 18668289261 浙江省 宁波市 海曙区 高桥镇高强路8号吉秀制刷</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -946,11 +972,7 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>含税含运含进仓</t>
-        </is>
-      </c>
+      <c r="B13" s="25" t="inlineStr"/>
       <c r="C13" s="25" t="n"/>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n"/>
@@ -974,7 +996,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>45天</t>
+          <t>15天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1041,11 +1063,7 @@
       <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>宁波市海曙区高桥镇秀丰路67号1栋1楼，小张，18668289261</t>
-        </is>
-      </c>
+      <c r="A19" s="25" t="inlineStr"/>
       <c r="B19" s="25" t="n"/>
       <c r="C19" s="25" t="n"/>
       <c r="D19" s="25" t="n"/>
@@ -1320,7 +1338,7 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>宁波瑾秀制刷科技有限公司</t>
+          <t>和鑫制刷厂</t>
         </is>
       </c>
       <c r="F69" s="9" t="n"/>
@@ -1369,5 +1387,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.78740157480315" bottom="0.590551181102362" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="65" horizontalDpi="360" verticalDpi="360"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>